--- a/LyapunovDataSet.xlsx
+++ b/LyapunovDataSet.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C2790A-85CB-4C87-A0B8-71B1DD2EF6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5E2D6713-B345-41D2-9A91-FA35AFDFA91A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5E2D6713-B345-41D2-9A91-FA35AFDFA91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
